--- a/artifacts/central-inventory/verified-export.xlsx
+++ b/artifacts/central-inventory/verified-export.xlsx
@@ -88,7 +88,7 @@
     <t>Generated at (UTC)</t>
   </si>
   <si>
-    <t>2026-10-04T14:14:49.458Z</t>
+    <t>2026-10-07T23:19:42.856Z</t>
   </si>
   <si>
     <t>Summary</t>
